--- a/data/Data_dictionary.xlsx
+++ b/data/Data_dictionary.xlsx
@@ -5,16 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jvega\Desktop\PRACTICAS\SHOPFULLY\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jvega\Desktop\PRACTICAS\SHOPFULLY\project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8CAF95-FA47-40C6-AB27-F46AE6582D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED7791-4197-4D74-8117-56003998E45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F062C93-53EF-4F65-AB22-B06D23354122}"/>
   </bookViews>
   <sheets>
     <sheet name="CLEAN" sheetId="1" r:id="rId1"/>
-    <sheet name="RAW AND REJECTED" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -373,10 +372,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,22 +725,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -934,17 +933,17 @@
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -1102,17 +1101,17 @@
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -1274,13 +1273,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154A2CEE-B490-490B-AC90-3FC51472F9DB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>